--- a/Catalogo_Unidades_Admvas.xlsx
+++ b/Catalogo_Unidades_Admvas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unidades Admvas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Unidades Admvas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,15 @@
     <font>
       <name val="Calibri"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="7">
@@ -113,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -132,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -498,24 +513,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CATÁLOGO DE UNIDADES ADMINISTRATIVAS — Registro Estatal de Servidores Públicos</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>CATÁLOGO DE UNIDADES ADMINISTRATIVAS – Registro Estatal de Servidores Públicos</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  Azul oscuro = Obligatorio  |  Datos desde fila 4  |  Clave_Unidad = 8 dígitos: 2 depcia + 2 unidad + 2 subunidad + 2 nivel</t>
         </is>
@@ -524,20 +538,15 @@
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>EJERCICIO</t>
+          <t>Depcia</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Depcia</t>
+          <t>Clave_Unidad</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Clave_Unidad</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Descripción_unidad</t>
         </is>
@@ -546,220 +555,185 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ej: 01</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Ej: 01</t>
+          <t>Ej: 01020201</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Ej: 01020201</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
           <t>Ej: OFICINA DEL INSTITUTO DE LA DEFENSORIA PUBLICA</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="5" t="n">
-        <v>2025</v>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
+          <t>01020201</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>OFICINA DEL SECRETARIO DE GOBIERNO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>01020201</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>OFICINA DEL SECRETARIO DE GOBIERNO</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="6" t="n">
-        <v>2025</v>
-      </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
+          <t>01350101</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>OFICINA DEL INSTITUTO DE LA DEFENSORIA PUBLICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>01350101</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>OFICINA DEL INSTITUTO DE LA DEFENSORIA PUBLICA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>2025</v>
-      </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
+          <t>01360101</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>OFICINA DE LA COMISION EJECUTIVA ESTATAL DE ATENCION A VICTIMAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>01360101</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>OFICINA DE LA COMISION EJECUTIVA ESTATAL DE ATENCION A VICTIMAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2025</v>
-      </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>01370101</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>01370101</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
           <t>OFICINA DE LA DIRECCION GENERAL DEL SERVICIO ESTATAL DE EMPLEO</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>2025</v>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>04010101</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>04010101</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
           <t>OFICINA DEL SECRETARIO DE SEGURIDAD</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>2025</v>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>07010101</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>07010101</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
           <t>OFICINA DEL SECRETARIO DE EDUCACION</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>2025</v>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>08010101</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>08010101</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
           <t>OFICINA DEL SECRETARIO DE SALUD</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="6" t="n">
-        <v>2025</v>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
+          <t>21010101</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>OFICINA DEL OFICIAL MAYOR DE GOBIERNO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>21010101</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>OFICINA DEL OFICIAL MAYOR DE GOBIERNO</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>2025</v>
-      </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>21060301</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>21060301</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
           <t>SUBDIRECCION DE ADMINISTRACION DE SISTEMA DE NOMINA</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>2025</v>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>98010101</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>98010101</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>OFICINA DEL DIRECTOR GENERAL DEL ITAPET</t>
         </is>
@@ -767,8 +741,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
